--- a/src/data/game_data.xlsx
+++ b/src/data/game_data.xlsx
@@ -713,7 +713,7 @@
         <v>["Mohism","Siege Defense"]</v>
       </c>
       <c r="H12" t="str">
-        <v>/portraits/qinhuali.png</v>
+        <v>/portraits/qinguli.png</v>
       </c>
     </row>
     <row r="13">
@@ -921,7 +921,7 @@
         <v>["Legalism","Centralization"]</v>
       </c>
       <c r="H20" t="str">
-        <v>/portraits/lishi.png</v>
+        <v>/portraits/lisi.png</v>
       </c>
     </row>
     <row r="21">
@@ -1623,7 +1623,7 @@
         <v>["Agriculturalism"]</v>
       </c>
       <c r="H47" t="str">
-        <v>/portraits/xuhing.png</v>
+        <v>/portraits/xuxing.png</v>
       </c>
     </row>
     <row r="48">
